--- a/20260512_银河.xlsx
+++ b/20260512_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>710</v>
+        <v>709.2</v>
       </c>
       <c r="D2" s="1">
-        <v>-1</v>
+        <v>-1.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0014</v>
+        <v>-0.0025</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-1.1</v>
+        <v>-1.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0015</v>
+        <v>-0.0027</v>
       </c>
       <c r="L2" s="1">
-        <v>-1.1</v>
+        <v>-1.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0015</v>
+        <v>-0.0027</v>
       </c>
       <c r="N2" s="1">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="O2" s="1">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="P2" s="1">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0014</v>
+        <v>-0.0025</v>
       </c>
       <c r="U2" s="5">
-        <v>3.55</v>
+        <v>3.546</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0017</v>
+        <v>0.0028</v>
       </c>
       <c r="X2" s="2">
-        <v>0.109</v>
+        <v>0.1078</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0748</v>
+        <v>0.0736</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1776</v>
+        <v>0.1763</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4748</v>
+        <v>0.4732</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>867.6</v>
+        <v>866</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0023</v>
+        <v>0.0005</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0054</v>
+        <v>0.0036</v>
       </c>
       <c r="L3" s="1">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0054</v>
+        <v>0.0036</v>
       </c>
       <c r="N3" s="1">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O3" s="1">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="1">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" s="2">
         <v>0.029</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0023</v>
+        <v>0.0005</v>
       </c>
       <c r="U3" s="5">
-        <v>2.169</v>
+        <v>2.165</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0418</v>
+        <v>0.0399</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0916</v>
+        <v>0.0896</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0999</v>
+        <v>0.0979</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1332</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>740.3</v>
+        <v>739.2</v>
       </c>
       <c r="D4" s="1">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.0028</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.0028</v>
+      </c>
+      <c r="N4" s="1">
         <v>3.2</v>
       </c>
-      <c r="K4" s="2">
-        <v>0.0043</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="O4" s="1">
         <v>3.2</v>
       </c>
-      <c r="M4" s="2">
-        <v>0.0043</v>
-      </c>
-      <c r="N4" s="1">
-        <v>2.1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>2.1</v>
-      </c>
       <c r="P4" s="1">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.673</v>
+        <v>0.672</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0483</v>
+        <v>0.0467</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0843</v>
+        <v>-0.0857</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1762</v>
+        <v>-0.1775</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0665</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>994.2</v>
+        <v>994</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="2">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0029</v>
+        <v>0.0027</v>
       </c>
       <c r="L5" s="1">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0029</v>
+        <v>0.0027</v>
       </c>
       <c r="N5" s="1">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="O5" s="1">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="P5" s="1">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0332</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="U5" s="5">
-        <v>4.971</v>
+        <v>4.97</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0709</v>
+        <v>0.0707</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0526</v>
+        <v>0.0523</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0708</v>
+        <v>0.0706</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.322</v>
+        <v>0.3218</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>986.9</v>
+        <v>985.8</v>
       </c>
       <c r="D6" s="1">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0097</v>
+        <v>0.0086</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0136</v>
+        <v>0.0124</v>
       </c>
       <c r="L6" s="1">
-        <v>13.2</v>
+        <v>12.1</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0136</v>
+        <v>0.0124</v>
       </c>
       <c r="N6" s="1">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="1">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="P6" s="1">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0097</v>
+        <v>0.0086</v>
       </c>
       <c r="U6" s="5">
-        <v>9.869</v>
+        <v>9.858</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0104</v>
+        <v>-0.0115</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0827</v>
+        <v>-0.0837</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0891</v>
+        <v>0.0879</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3104</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1009</v>
+        <v>0.101</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>790.2</v>
+        <v>790.8</v>
       </c>
       <c r="D8" s="1">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.001</v>
+        <v>0.0018</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0044</v>
+        <v>0.0052</v>
       </c>
       <c r="L8" s="1">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0044</v>
+        <v>0.0052</v>
       </c>
       <c r="N8" s="1">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="O8" s="1">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="P8" s="1">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.001</v>
+        <v>0.0018</v>
       </c>
       <c r="U8" s="5">
-        <v>3.951</v>
+        <v>3.954</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1496</v>
+        <v>0.1504</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2071</v>
+        <v>0.208</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2692</v>
+        <v>0.2701</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9914</v>
+        <v>0.9929</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20262.2</v>
+        <v>20246.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-85.4</v>
+        <v>-100.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0042</v>
+        <v>-0.005</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-115.44</v>
+        <v>-130.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0057</v>
+        <v>-0.0064</v>
       </c>
       <c r="L9" s="1">
-        <v>-115.44</v>
+        <v>-130.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0057</v>
+        <v>-0.0064</v>
       </c>
       <c r="N9" s="1">
-        <v>-112.64</v>
+        <v>-126.64</v>
       </c>
       <c r="O9" s="1">
-        <v>-112.64</v>
+        <v>-126.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-112.64</v>
+        <v>-126.64</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6772</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0042</v>
+        <v>-0.005</v>
       </c>
       <c r="U9" s="5">
-        <v>14.473</v>
+        <v>14.462</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0057</v>
+        <v>0.0064</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0352</v>
+        <v>0.0344</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.009</v>
+        <v>-0.0097</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0607</v>
+        <v>0.0599</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2118</v>
+        <v>0.2109</v>
       </c>
     </row>
     <row r="10">
@@ -1229,16 +1229,16 @@
         <v>-0.0097</v>
       </c>
       <c r="N10" s="1">
-        <v>-6.9</v>
+        <v>-6.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-6.9</v>
+        <v>-6.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-6.9</v>
+        <v>-6.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0222</v>
+        <v>0.0223</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>876.4</v>
+        <v>874.8</v>
       </c>
       <c r="D11" s="1">
-        <v>16.8</v>
+        <v>15.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0195</v>
+        <v>0.0177</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>15.9</v>
+        <v>14.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0185</v>
+        <v>0.0166</v>
       </c>
       <c r="L11" s="1">
-        <v>15.9</v>
+        <v>14.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0185</v>
+        <v>0.0166</v>
       </c>
       <c r="N11" s="1">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="O11" s="1">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="P11" s="1">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0293</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0195</v>
+        <v>0.0177</v>
       </c>
       <c r="U11" s="5">
-        <v>2.191</v>
+        <v>2.187</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.073</v>
+        <v>0.071</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0398</v>
+        <v>0.0379</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2092</v>
+        <v>0.207</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3247</v>
+        <v>0.3223</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29912</v>
+        <v>29890.8</v>
       </c>
       <c r="D12" s="1">
-        <v>-52.6</v>
+        <v>-73.8</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0018</v>
+        <v>-0.0025</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-79.79</v>
+        <v>-100.99</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0027</v>
+        <v>-0.0034</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-74.99</v>
+        <v>-96.59</v>
       </c>
       <c r="O12" s="1">
-        <v>-74.99</v>
+        <v>-96.59</v>
       </c>
       <c r="P12" s="1">
-        <v>-74.99</v>
+        <v>-96.59</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/20260512_银河.xlsx
+++ b/20260512_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>709.2</v>
+        <v>708.6</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0025</v>
+        <v>-0.0034</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
+        <v>-2.5</v>
+      </c>
+      <c r="K2" s="2">
+        <v>-0.0035</v>
+      </c>
+      <c r="L2" s="1">
+        <v>-2.5</v>
+      </c>
+      <c r="M2" s="2">
+        <v>-0.0035</v>
+      </c>
+      <c r="N2" s="1">
         <v>-1.9</v>
       </c>
-      <c r="K2" s="2">
-        <v>-0.0027</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="O2" s="1">
         <v>-1.9</v>
       </c>
-      <c r="M2" s="2">
-        <v>-0.0027</v>
-      </c>
-      <c r="N2" s="1">
-        <v>-1.7</v>
-      </c>
-      <c r="O2" s="1">
-        <v>-1.7</v>
-      </c>
       <c r="P2" s="1">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0025</v>
+        <v>-0.0034</v>
       </c>
       <c r="U2" s="5">
-        <v>3.546</v>
+        <v>3.543</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0028</v>
+        <v>0.0037</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1078</v>
+        <v>0.1069</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0736</v>
+        <v>0.0727</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1763</v>
+        <v>0.1753</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4732</v>
+        <v>0.4719</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866</v>
+        <v>866.4</v>
       </c>
       <c r="D3" s="1">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0036</v>
+        <v>0.0041</v>
       </c>
       <c r="L3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0036</v>
+        <v>0.0041</v>
       </c>
       <c r="N3" s="1">
         <v>3.5</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="U3" s="5">
-        <v>2.165</v>
+        <v>2.166</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0399</v>
+        <v>0.0404</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0896</v>
+        <v>0.0901</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0979</v>
+        <v>0.0984</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1311</v>
+        <v>0.1316</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>739.2</v>
+        <v>737</v>
       </c>
       <c r="D4" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="K4" s="2">
-        <v>0.0028</v>
+        <v>-0.0001</v>
       </c>
       <c r="L4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="M4" s="2">
-        <v>0.0028</v>
+        <v>-0.0001</v>
       </c>
       <c r="N4" s="1">
-        <v>3.2</v>
+        <v>-1.2</v>
       </c>
       <c r="O4" s="1">
-        <v>3.2</v>
+        <v>-1.2</v>
       </c>
       <c r="P4" s="1">
-        <v>3.2</v>
+        <v>-1.2</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="U4" s="5">
-        <v>0.672</v>
+        <v>0.67</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0467</v>
+        <v>0.0436</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0857</v>
+        <v>-0.0884</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1775</v>
+        <v>-0.1799</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0679</v>
+        <v>-0.0707</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>994</v>
+        <v>993.8</v>
       </c>
       <c r="D5" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0008</v>
+        <v>0.0006</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.0025</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0.0025</v>
+      </c>
+      <c r="N5" s="1">
         <v>2.7</v>
       </c>
-      <c r="K5" s="2">
-        <v>0.0027</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="O5" s="1">
         <v>2.7</v>
       </c>
-      <c r="M5" s="2">
-        <v>0.0027</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1.7</v>
-      </c>
       <c r="P5" s="1">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0332</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0008</v>
+        <v>0.0006</v>
       </c>
       <c r="U5" s="5">
-        <v>4.97</v>
+        <v>4.969</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0707</v>
+        <v>0.0704</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0523</v>
+        <v>0.0521</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0706</v>
+        <v>0.0703</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3218</v>
+        <v>0.3215</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>985.8</v>
+        <v>986.4</v>
       </c>
       <c r="D6" s="1">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0086</v>
+        <v>0.0092</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0124</v>
+        <v>0.013</v>
       </c>
       <c r="L6" s="1">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0124</v>
+        <v>0.013</v>
       </c>
       <c r="N6" s="1">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="O6" s="1">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="P6" s="1">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0086</v>
+        <v>0.0092</v>
       </c>
       <c r="U6" s="5">
-        <v>9.858</v>
+        <v>9.864</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0115</v>
+        <v>-0.0109</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0837</v>
+        <v>-0.0831</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0879</v>
+        <v>0.0885</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.309</v>
+        <v>0.3098</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>790.8</v>
+        <v>789.2</v>
       </c>
       <c r="D8" s="1">
-        <v>1.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0018</v>
+        <v>-0.0003</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0052</v>
+        <v>0.0032</v>
       </c>
       <c r="L8" s="1">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0052</v>
+        <v>0.0032</v>
       </c>
       <c r="N8" s="1">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="O8" s="1">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="P8" s="1">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0018</v>
+        <v>-0.0003</v>
       </c>
       <c r="U8" s="5">
-        <v>3.954</v>
+        <v>3.946</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1504</v>
+        <v>0.1481</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.208</v>
+        <v>0.2056</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2701</v>
+        <v>0.2676</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9929</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="9">
@@ -1113,10 +1113,10 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20246.8</v>
+        <v>20245.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-100.8</v>
+        <v>-102.2</v>
       </c>
       <c r="E9" s="2">
         <v>-0.005</v>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-130.84</v>
+        <v>-132.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0064</v>
+        <v>-0.0065</v>
       </c>
       <c r="L9" s="1">
-        <v>-130.84</v>
+        <v>-132.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0064</v>
+        <v>-0.0065</v>
       </c>
       <c r="N9" s="1">
-        <v>-126.64</v>
+        <v>-133.64</v>
       </c>
       <c r="O9" s="1">
-        <v>-126.64</v>
+        <v>-133.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-126.64</v>
+        <v>-133.64</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6772</v>
+        <v>0.6773</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1167,25 +1167,25 @@
         <v>-0.005</v>
       </c>
       <c r="U9" s="5">
-        <v>14.462</v>
+        <v>14.461</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0064</v>
+        <v>0.0065</v>
       </c>
       <c r="X9" s="2">
         <v>0.0344</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0097</v>
+        <v>-0.0098</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0599</v>
+        <v>0.0598</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2109</v>
+        <v>0.2108</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>665.6</v>
+        <v>666</v>
       </c>
       <c r="D10" s="1">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0006</v>
+        <v>0.0012</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.5</v>
+        <v>-6.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0091</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.5</v>
+        <v>-6.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0097</v>
+        <v>-0.0091</v>
       </c>
       <c r="N10" s="1">
         <v>-6.1</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0006</v>
+        <v>0.0012</v>
       </c>
       <c r="U10" s="5">
-        <v>1.664</v>
+        <v>1.665</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0096</v>
+        <v>0.009</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0303</v>
+        <v>0.0309</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.286</v>
+        <v>0.2867</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3673</v>
+        <v>0.3681</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.3031</v>
+        <v>0.3039</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>874.8</v>
+        <v>872</v>
       </c>
       <c r="D11" s="1">
-        <v>15.2</v>
+        <v>12.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0177</v>
+        <v>0.0144</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0166</v>
+        <v>0.0134</v>
       </c>
       <c r="L11" s="1">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0166</v>
+        <v>0.0134</v>
       </c>
       <c r="N11" s="1">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
       <c r="O11" s="1">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
       <c r="P11" s="1">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0177</v>
+        <v>0.0144</v>
       </c>
       <c r="U11" s="5">
-        <v>2.187</v>
+        <v>2.18</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.071</v>
+        <v>0.0676</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0379</v>
+        <v>0.0346</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.207</v>
+        <v>0.2031</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3223</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29890.8</v>
+        <v>29883.4</v>
       </c>
       <c r="D12" s="1">
-        <v>-73.8</v>
+        <v>-81.2</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0025</v>
+        <v>-0.0027</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-100.99</v>
+        <v>-108.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0034</v>
+        <v>-0.0036</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-96.59</v>
+        <v>-110.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-96.59</v>
+        <v>-110.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-96.59</v>
+        <v>-110.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/20260512_银河.xlsx
+++ b/20260512_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>708.6</v>
+        <v>708</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0034</v>
+        <v>-0.0042</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-2.5</v>
+        <v>-3.1</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0035</v>
+        <v>-0.0044</v>
       </c>
       <c r="L2" s="1">
-        <v>-2.5</v>
+        <v>-3.1</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0035</v>
+        <v>-0.0044</v>
       </c>
       <c r="N2" s="1">
-        <v>-1.9</v>
+        <v>-2.7</v>
       </c>
       <c r="O2" s="1">
-        <v>-1.9</v>
+        <v>-2.7</v>
       </c>
       <c r="P2" s="1">
-        <v>-1.9</v>
+        <v>-2.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0034</v>
+        <v>-0.0042</v>
       </c>
       <c r="U2" s="5">
-        <v>3.543</v>
+        <v>3.54</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0037</v>
+        <v>0.0045</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1069</v>
+        <v>0.1059</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0727</v>
+        <v>0.0718</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1753</v>
+        <v>0.1743</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4719</v>
+        <v>0.4707</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866.4</v>
+        <v>866</v>
       </c>
       <c r="D3" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0041</v>
+        <v>0.0036</v>
       </c>
       <c r="L3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0041</v>
+        <v>0.0036</v>
       </c>
       <c r="N3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P3" s="1">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" s="2">
         <v>0.029</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="U3" s="5">
-        <v>2.166</v>
+        <v>2.165</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0404</v>
+        <v>0.0399</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0901</v>
+        <v>0.0896</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0984</v>
+        <v>0.0979</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1316</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>737</v>
+        <v>739.2</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-0.1</v>
+        <v>2.1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0001</v>
+        <v>0.0028</v>
       </c>
       <c r="L4" s="1">
-        <v>-0.1</v>
+        <v>2.1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0001</v>
+        <v>0.0028</v>
       </c>
       <c r="N4" s="1">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
       <c r="O4" s="1">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
       <c r="P4" s="1">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.67</v>
+        <v>0.672</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0436</v>
+        <v>0.0467</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0884</v>
+        <v>-0.0857</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1799</v>
+        <v>-0.1775</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0707</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>993.8</v>
+        <v>994</v>
       </c>
       <c r="D5" s="1">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0006</v>
+        <v>0.0008</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="L5" s="1">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0025</v>
+        <v>0.0027</v>
       </c>
       <c r="N5" s="1">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O5" s="1">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="P5" s="1">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0332</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0006</v>
+        <v>0.0008</v>
       </c>
       <c r="U5" s="5">
-        <v>4.969</v>
+        <v>4.97</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0704</v>
+        <v>0.0707</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0521</v>
+        <v>0.0523</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0703</v>
+        <v>0.0706</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3215</v>
+        <v>0.3218</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>986.4</v>
+        <v>985.9</v>
       </c>
       <c r="D6" s="1">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0092</v>
+        <v>0.0087</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="K6" s="2">
-        <v>0.013</v>
+        <v>0.0125</v>
       </c>
       <c r="L6" s="1">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="M6" s="2">
-        <v>0.013</v>
+        <v>0.0125</v>
       </c>
       <c r="N6" s="1">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="O6" s="1">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="P6" s="1">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0092</v>
+        <v>0.0087</v>
       </c>
       <c r="U6" s="5">
-        <v>9.864</v>
+        <v>9.859</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0109</v>
+        <v>-0.0114</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0831</v>
+        <v>-0.0836</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0885</v>
+        <v>0.088</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3098</v>
+        <v>0.3091</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>-0.15</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.101</v>
+        <v>0.1009</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>789.2</v>
+        <v>790.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0032</v>
+        <v>0.0047</v>
       </c>
       <c r="L8" s="1">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0032</v>
+        <v>0.0047</v>
       </c>
       <c r="N8" s="1">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="O8" s="1">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="P8" s="1">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="U8" s="5">
-        <v>3.946</v>
+        <v>3.952</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1481</v>
+        <v>0.1499</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2056</v>
+        <v>0.2074</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2676</v>
+        <v>0.2695</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9889</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20245.4</v>
+        <v>20255.2</v>
       </c>
       <c r="D9" s="1">
-        <v>-102.2</v>
+        <v>-92.4</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.005</v>
+        <v>-0.0045</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-132.24</v>
+        <v>-122.44</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0065</v>
+        <v>-0.006</v>
       </c>
       <c r="L9" s="1">
-        <v>-132.24</v>
+        <v>-122.44</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0065</v>
+        <v>-0.006</v>
       </c>
       <c r="N9" s="1">
-        <v>-133.64</v>
+        <v>-140.64</v>
       </c>
       <c r="O9" s="1">
-        <v>-133.64</v>
+        <v>-140.64</v>
       </c>
       <c r="P9" s="1">
-        <v>-133.64</v>
+        <v>-140.64</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6773</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.005</v>
+        <v>-0.0045</v>
       </c>
       <c r="U9" s="5">
-        <v>14.461</v>
+        <v>14.468</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0065</v>
+        <v>0.006</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0344</v>
+        <v>0.0349</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0098</v>
+        <v>-0.0093</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0598</v>
+        <v>0.0604</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2108</v>
+        <v>0.2114</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>666</v>
+        <v>667.6</v>
       </c>
       <c r="D10" s="1">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0012</v>
+        <v>0.0036</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.1</v>
+        <v>-4.5</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0067</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.1</v>
+        <v>-4.5</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0067</v>
       </c>
       <c r="N10" s="1">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="O10" s="1">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="P10" s="1">
-        <v>-6.1</v>
+        <v>-5.7</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0223</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0012</v>
+        <v>0.0036</v>
       </c>
       <c r="U10" s="5">
-        <v>1.665</v>
+        <v>1.669</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.009</v>
+        <v>0.0066</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0309</v>
+        <v>0.0334</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2867</v>
+        <v>0.2898</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3681</v>
+        <v>0.3714</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.3039</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>872</v>
+        <v>872.8</v>
       </c>
       <c r="D11" s="1">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0144</v>
+        <v>0.0154</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0134</v>
+        <v>0.0143</v>
       </c>
       <c r="L11" s="1">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0134</v>
+        <v>0.0143</v>
       </c>
       <c r="N11" s="1">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="O11" s="1">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="P11" s="1">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0292</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0144</v>
+        <v>0.0154</v>
       </c>
       <c r="U11" s="5">
-        <v>2.18</v>
+        <v>2.182</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0676</v>
+        <v>0.0686</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0346</v>
+        <v>0.0356</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2031</v>
+        <v>0.2042</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.318</v>
+        <v>0.3193</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29883.4</v>
+        <v>29897.7</v>
       </c>
       <c r="D12" s="1">
-        <v>-81.2</v>
+        <v>-66.9</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0027</v>
+        <v>-0.0022</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-108.39</v>
+        <v>-94.09</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0036</v>
+        <v>-0.0031</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-110.69</v>
+        <v>-117.09</v>
       </c>
       <c r="O12" s="1">
-        <v>-110.69</v>
+        <v>-117.09</v>
       </c>
       <c r="P12" s="1">
-        <v>-110.69</v>
+        <v>-117.09</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>

--- a/20260512_银河.xlsx
+++ b/20260512_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>708</v>
+        <v>709.2</v>
       </c>
       <c r="D2" s="1">
-        <v>-3</v>
+        <v>-1.8</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0042</v>
+        <v>-0.0025</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0044</v>
+        <v>-0.0027</v>
       </c>
       <c r="L2" s="1">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0044</v>
+        <v>-0.0027</v>
       </c>
       <c r="N2" s="1">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="O2" s="1">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="P2" s="1">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0042</v>
+        <v>-0.0025</v>
       </c>
       <c r="U2" s="5">
-        <v>3.54</v>
+        <v>3.546</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0045</v>
+        <v>0.0028</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1059</v>
+        <v>0.1078</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0718</v>
+        <v>0.0736</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1743</v>
+        <v>0.1763</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4707</v>
+        <v>0.4732</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>866</v>
+        <v>864.4</v>
       </c>
       <c r="D3" s="1">
-        <v>0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0005</v>
+        <v>-0.0014</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0036</v>
+        <v>0.0017</v>
       </c>
       <c r="L3" s="1">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0036</v>
+        <v>0.0017</v>
       </c>
       <c r="N3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P3" s="1">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.029</v>
+        <v>0.0289</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0005</v>
+        <v>-0.0014</v>
       </c>
       <c r="U3" s="5">
-        <v>2.165</v>
+        <v>2.161</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.0399</v>
+        <v>0.038</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0896</v>
+        <v>0.0876</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0979</v>
+        <v>0.0959</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.1311</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>739.2</v>
+        <v>740.3</v>
       </c>
       <c r="D4" s="1">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="E4" s="2">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.0043</v>
+      </c>
+      <c r="L4" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.0043</v>
+      </c>
+      <c r="N4" s="1">
         <v>2.1</v>
       </c>
-      <c r="K4" s="2">
-        <v>0.0028</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="O4" s="1">
         <v>2.1</v>
       </c>
-      <c r="M4" s="2">
-        <v>0.0028</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
       <c r="P4" s="1">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.003</v>
+        <v>0.0045</v>
       </c>
       <c r="U4" s="5">
-        <v>0.672</v>
+        <v>0.673</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0467</v>
+        <v>0.0483</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0857</v>
+        <v>-0.0843</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1775</v>
+        <v>-0.1762</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0679</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>994</v>
+        <v>995.6</v>
       </c>
       <c r="D5" s="1">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0008</v>
+        <v>0.0024</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0027</v>
+        <v>0.0043</v>
       </c>
       <c r="L5" s="1">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0027</v>
+        <v>0.0043</v>
       </c>
       <c r="N5" s="1">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O5" s="1">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="P5" s="1">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0332</v>
+        <v>0.0333</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0008</v>
+        <v>0.0024</v>
       </c>
       <c r="U5" s="5">
-        <v>4.97</v>
+        <v>4.978</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0707</v>
+        <v>0.0724</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0523</v>
+        <v>0.054</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0706</v>
+        <v>0.0723</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3218</v>
+        <v>0.3239</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>985.9</v>
+        <v>986.1</v>
       </c>
       <c r="D6" s="1">
-        <v>8.5</v>
+        <v>8.7</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0087</v>
+        <v>0.0089</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0125</v>
+        <v>0.0127</v>
       </c>
       <c r="L6" s="1">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0125</v>
+        <v>0.0127</v>
       </c>
       <c r="N6" s="1">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="1">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="P6" s="1">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0087</v>
+        <v>0.0089</v>
       </c>
       <c r="U6" s="5">
-        <v>9.859</v>
+        <v>9.861</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0114</v>
+        <v>-0.0112</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0836</v>
+        <v>-0.0834</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.088</v>
+        <v>0.0882</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3091</v>
+        <v>0.3094</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>790.4</v>
+        <v>791.6</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0013</v>
+        <v>0.0028</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0047</v>
+        <v>0.0062</v>
       </c>
       <c r="L8" s="1">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0047</v>
+        <v>0.0062</v>
       </c>
       <c r="N8" s="1">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="O8" s="1">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="P8" s="1">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0264</v>
+        <v>0.0265</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0013</v>
+        <v>0.0028</v>
       </c>
       <c r="U8" s="5">
-        <v>3.952</v>
+        <v>3.958</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1499</v>
+        <v>0.1516</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2074</v>
+        <v>0.2093</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2695</v>
+        <v>0.2714</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9919</v>
+        <v>0.9949</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20255.2</v>
+        <v>20267.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-92.4</v>
+        <v>-79.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0045</v>
+        <v>-0.0039</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-122.44</v>
+        <v>-109.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.006</v>
+        <v>-0.0054</v>
       </c>
       <c r="L9" s="1">
-        <v>-122.44</v>
+        <v>-109.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.006</v>
+        <v>-0.0054</v>
       </c>
       <c r="N9" s="1">
-        <v>-140.64</v>
+        <v>-129.44</v>
       </c>
       <c r="O9" s="1">
-        <v>-140.64</v>
+        <v>-129.44</v>
       </c>
       <c r="P9" s="1">
-        <v>-140.64</v>
+        <v>-129.44</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6773</v>
+        <v>0.6774</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0045</v>
+        <v>-0.0039</v>
       </c>
       <c r="U9" s="5">
-        <v>14.468</v>
+        <v>14.477</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.006</v>
+        <v>0.0054</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0349</v>
+        <v>0.0355</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0093</v>
+        <v>-0.0087</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0604</v>
+        <v>0.061</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2114</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>667.6</v>
+        <v>666</v>
       </c>
       <c r="D10" s="1">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0036</v>
+        <v>0.0012</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-4.5</v>
+        <v>-6.1</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0067</v>
+        <v>-0.0091</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.5</v>
+        <v>-6.1</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0067</v>
+        <v>-0.0091</v>
       </c>
       <c r="N10" s="1">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="O10" s="1">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="P10" s="1">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0223</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0036</v>
+        <v>0.0012</v>
       </c>
       <c r="U10" s="5">
-        <v>1.669</v>
+        <v>1.665</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0066</v>
+        <v>0.009</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0334</v>
+        <v>0.0309</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2898</v>
+        <v>0.2867</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3714</v>
+        <v>0.3681</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.307</v>
+        <v>0.3039</v>
       </c>
     </row>
     <row r="11">
@@ -1312,13 +1312,13 @@
         <v>0.0143</v>
       </c>
       <c r="N11" s="1">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="O11" s="1">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="P11" s="1">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0292</v>
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29897.7</v>
+        <v>29912.4</v>
       </c>
       <c r="D12" s="1">
-        <v>-66.9</v>
+        <v>-52.2</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0022</v>
+        <v>-0.0017</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-94.09</v>
+        <v>-79.39</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0031</v>
+        <v>-0.0026</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-117.09</v>
+        <v>-101.89</v>
       </c>
       <c r="O12" s="1">
-        <v>-117.09</v>
+        <v>-101.89</v>
       </c>
       <c r="P12" s="1">
-        <v>-117.09</v>
+        <v>-101.89</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>
@@ -1499,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1538,34 +1538,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-06</v>
       </c>
       <c r="B2" t="str">
-        <v>14:02:01</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>510300</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>300ETF</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>买入</v>
+        <v>银行转证券</v>
       </c>
       <c r="F2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>4.956</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-991.3</v>
-      </c>
-      <c r="I2" s="6">
-        <v>991.2</v>
-      </c>
-      <c r="J2" s="6">
-        <v>0.1</v>
+        <v>15000</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -1576,31 +1570,25 @@
         <v>2026-05-11</v>
       </c>
       <c r="B3" t="str">
-        <v>14:02:37</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>512100</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>1000ETF</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>买入</v>
+        <v>银行转证券</v>
       </c>
       <c r="F3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>3.555</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-711.1</v>
-      </c>
-      <c r="I3" s="6">
-        <v>711</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0.1</v>
+        <v>15000</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -1611,13 +1599,13 @@
         <v>2026-05-11</v>
       </c>
       <c r="B4" t="str">
-        <v>14:02:50</v>
+        <v>14:02:01</v>
       </c>
       <c r="C4" t="str">
-        <v>159915</v>
+        <v>510300</v>
       </c>
       <c r="D4" t="str">
-        <v>创业板</v>
+        <v>300ETF</v>
       </c>
       <c r="E4" t="str">
         <v>买入</v>
@@ -1626,13 +1614,13 @@
         <v>200</v>
       </c>
       <c r="G4">
-        <v>3.933</v>
+        <v>4.956</v>
       </c>
       <c r="H4">
-        <v>-786.7</v>
+        <v>-991.3</v>
       </c>
       <c r="I4" s="6">
-        <v>786.6</v>
+        <v>991.2</v>
       </c>
       <c r="J4" s="6">
         <v>0.1</v>
@@ -1646,28 +1634,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B5" t="str">
-        <v>14:03:06</v>
+        <v>14:02:37</v>
       </c>
       <c r="C5" t="str">
-        <v>513010</v>
+        <v>512100</v>
       </c>
       <c r="D5" t="str">
-        <v>港股科技</v>
+        <v>1000ETF</v>
       </c>
       <c r="E5" t="str">
         <v>买入</v>
       </c>
       <c r="F5">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="G5">
-        <v>0.67</v>
+        <v>3.555</v>
       </c>
       <c r="H5">
-        <v>-737.1</v>
+        <v>-711.1</v>
       </c>
       <c r="I5" s="6">
-        <v>737</v>
+        <v>711</v>
       </c>
       <c r="J5" s="6">
         <v>0.1</v>
@@ -1681,28 +1669,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B6" t="str">
-        <v>14:03:51</v>
+        <v>14:02:50</v>
       </c>
       <c r="C6" t="str">
-        <v>518880</v>
+        <v>159915</v>
       </c>
       <c r="D6" t="str">
-        <v>黄金ETF</v>
+        <v>创业板</v>
       </c>
       <c r="E6" t="str">
         <v>买入</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G6">
-        <v>9.736</v>
+        <v>3.933</v>
       </c>
       <c r="H6">
-        <v>-973.7</v>
+        <v>-786.7</v>
       </c>
       <c r="I6" s="6">
-        <v>973.6</v>
+        <v>786.6</v>
       </c>
       <c r="J6" s="6">
         <v>0.1</v>
@@ -1716,28 +1704,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B7" t="str">
-        <v>14:04:05</v>
+        <v>14:03:06</v>
       </c>
       <c r="C7" t="str">
-        <v>159981</v>
+        <v>513010</v>
       </c>
       <c r="D7" t="str">
-        <v>能源化工</v>
+        <v>港股科技</v>
       </c>
       <c r="E7" t="str">
         <v>买入</v>
       </c>
       <c r="F7">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="G7">
-        <v>1.68</v>
+        <v>0.67</v>
       </c>
       <c r="H7">
-        <v>-672.1</v>
+        <v>-737.1</v>
       </c>
       <c r="I7" s="6">
-        <v>672</v>
+        <v>737</v>
       </c>
       <c r="J7" s="6">
         <v>0.1</v>
@@ -1751,28 +1739,28 @@
         <v>2026-05-11</v>
       </c>
       <c r="B8" t="str">
-        <v>14:04:16</v>
+        <v>14:03:51</v>
       </c>
       <c r="C8" t="str">
-        <v>159985</v>
+        <v>518880</v>
       </c>
       <c r="D8" t="str">
-        <v>豆粕ETF</v>
+        <v>黄金ETF</v>
       </c>
       <c r="E8" t="str">
         <v>买入</v>
       </c>
       <c r="F8">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>2.157</v>
+        <v>9.736</v>
       </c>
       <c r="H8">
-        <v>-862.9</v>
+        <v>-973.7</v>
       </c>
       <c r="I8" s="6">
-        <v>862.8</v>
+        <v>973.6</v>
       </c>
       <c r="J8" s="6">
         <v>0.1</v>
@@ -1786,31 +1774,31 @@
         <v>2026-05-11</v>
       </c>
       <c r="B9" t="str">
-        <v>14:04:34</v>
+        <v>14:04:05</v>
       </c>
       <c r="C9" t="str">
-        <v>511380</v>
+        <v>159981</v>
       </c>
       <c r="D9" t="str">
-        <v>转债ETF</v>
+        <v>能源化工</v>
       </c>
       <c r="E9" t="str">
         <v>买入</v>
       </c>
       <c r="F9">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="G9">
-        <v>14.554</v>
+        <v>1.68</v>
       </c>
       <c r="H9">
-        <v>-20377.64</v>
+        <v>-672.1</v>
       </c>
       <c r="I9" s="6">
-        <v>20375.6</v>
+        <v>672</v>
       </c>
       <c r="J9" s="6">
-        <v>2.04</v>
+        <v>0.1</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -1821,31 +1809,31 @@
         <v>2026-05-11</v>
       </c>
       <c r="B10" t="str">
-        <v>14:04:49</v>
+        <v>14:04:16</v>
       </c>
       <c r="C10" t="str">
-        <v>166016</v>
+        <v>159985</v>
       </c>
       <c r="D10" t="str">
-        <v>中欧纯债</v>
+        <v>豆粕ETF</v>
       </c>
       <c r="E10" t="str">
         <v>买入</v>
       </c>
       <c r="F10">
-        <v>2700</v>
+        <v>400</v>
       </c>
       <c r="G10">
-        <v>1.118</v>
+        <v>2.157</v>
       </c>
       <c r="H10">
-        <v>-3018.75</v>
+        <v>-862.9</v>
       </c>
       <c r="I10" s="6">
-        <v>3018.6</v>
+        <v>862.8</v>
       </c>
       <c r="J10" s="6">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -1856,40 +1844,110 @@
         <v>2026-05-11</v>
       </c>
       <c r="B11" t="str">
-        <v>14:05:33</v>
+        <v>14:04:34</v>
       </c>
       <c r="C11" t="str">
-        <v>159980</v>
+        <v>511380</v>
       </c>
       <c r="D11" t="str">
-        <v>有色ETF</v>
+        <v>转债ETF</v>
       </c>
       <c r="E11" t="str">
         <v>买入</v>
       </c>
       <c r="F11">
+        <v>1400</v>
+      </c>
+      <c r="G11">
+        <v>14.554</v>
+      </c>
+      <c r="H11">
+        <v>-20377.64</v>
+      </c>
+      <c r="I11" s="6">
+        <v>20375.6</v>
+      </c>
+      <c r="J11" s="6">
+        <v>2.04</v>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>14:04:49</v>
+      </c>
+      <c r="C12" t="str">
+        <v>166016</v>
+      </c>
+      <c r="D12" t="str">
+        <v>中欧纯债</v>
+      </c>
+      <c r="E12" t="str">
+        <v>买入</v>
+      </c>
+      <c r="F12">
+        <v>2700</v>
+      </c>
+      <c r="G12">
+        <v>1.118</v>
+      </c>
+      <c r="H12">
+        <v>-3018.75</v>
+      </c>
+      <c r="I12" s="6">
+        <v>3018.6</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>14:05:33</v>
+      </c>
+      <c r="C13" t="str">
+        <v>159980</v>
+      </c>
+      <c r="D13" t="str">
+        <v>有色ETF</v>
+      </c>
+      <c r="E13" t="str">
+        <v>买入</v>
+      </c>
+      <c r="F13">
         <v>400</v>
       </c>
-      <c r="G11">
+      <c r="G13">
         <v>2.151</v>
       </c>
-      <c r="H11">
+      <c r="H13">
         <v>-860.5</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I13" s="6">
         <v>860.4</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J13" s="6">
         <v>0.1</v>
       </c>
-      <c r="K11" t="str">
+      <c r="K13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/20260512_银河.xlsx
+++ b/20260512_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>709.2</v>
+        <v>709.6</v>
       </c>
       <c r="D2" s="1">
-        <v>-1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0025</v>
+        <v>-0.002</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0027</v>
+        <v>-0.0021</v>
       </c>
       <c r="L2" s="1">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0027</v>
+        <v>-0.0021</v>
       </c>
       <c r="N2" s="1">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
       <c r="O2" s="1">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
       <c r="P2" s="1">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0237</v>
@@ -583,28 +583,28 @@
         <v>2</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0025</v>
+        <v>-0.002</v>
       </c>
       <c r="U2" s="5">
-        <v>3.546</v>
+        <v>3.548</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0028</v>
+        <v>0.0023</v>
       </c>
       <c r="X2" s="2">
-        <v>0.1078</v>
+        <v>0.1084</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0736</v>
+        <v>0.0742</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1763</v>
+        <v>0.177</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4732</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>864.4</v>
+        <v>864</v>
       </c>
       <c r="D3" s="1">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0014</v>
+        <v>-0.0018</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,16 +636,16 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="K3" s="2">
-        <v>0.0017</v>
+        <v>0.0013</v>
       </c>
       <c r="L3" s="1">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="M3" s="2">
-        <v>0.0017</v>
+        <v>0.0013</v>
       </c>
       <c r="N3" s="1">
         <v>3.5</v>
@@ -666,10 +666,10 @@
         <v>2</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0014</v>
+        <v>-0.0018</v>
       </c>
       <c r="U3" s="5">
-        <v>2.161</v>
+        <v>2.16</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
@@ -678,16 +678,16 @@
         <v/>
       </c>
       <c r="X3" s="2">
-        <v>0.038</v>
+        <v>0.0375</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0876</v>
+        <v>0.0871</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0959</v>
+        <v>0.0954</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.129</v>
+        <v>0.1285</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>740.3</v>
+        <v>739.2</v>
       </c>
       <c r="D4" s="1">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="K4" s="2">
-        <v>0.0043</v>
+        <v>0.0028</v>
       </c>
       <c r="L4" s="1">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M4" s="2">
-        <v>0.0043</v>
+        <v>0.0028</v>
       </c>
       <c r="N4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="O4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="P4" s="1">
-        <v>2.1</v>
+        <v>-0.1</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0247</v>
@@ -749,10 +749,10 @@
         <v>2</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0045</v>
+        <v>0.003</v>
       </c>
       <c r="U4" s="5">
-        <v>0.673</v>
+        <v>0.672</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
@@ -761,16 +761,16 @@
         <v/>
       </c>
       <c r="X4" s="2">
-        <v>0.0483</v>
+        <v>0.0467</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0843</v>
+        <v>-0.0857</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1762</v>
+        <v>-0.1775</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0665</v>
+        <v>-0.0679</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>995.6</v>
+        <v>995.2</v>
       </c>
       <c r="D5" s="1">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0024</v>
+        <v>0.002</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K5" s="2">
-        <v>0.0043</v>
+        <v>0.0039</v>
       </c>
       <c r="L5" s="1">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="M5" s="2">
-        <v>0.0043</v>
+        <v>0.0039</v>
       </c>
       <c r="N5" s="1">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O5" s="1">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P5" s="1">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0333</v>
@@ -832,10 +832,10 @@
         <v>2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0024</v>
+        <v>0.002</v>
       </c>
       <c r="U5" s="5">
-        <v>4.978</v>
+        <v>4.976</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
@@ -844,16 +844,16 @@
         <v/>
       </c>
       <c r="X5" s="2">
-        <v>0.0724</v>
+        <v>0.072</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.054</v>
+        <v>0.0536</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0723</v>
+        <v>0.0719</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3239</v>
+        <v>0.3234</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>986.1</v>
+        <v>986.8</v>
       </c>
       <c r="D6" s="1">
-        <v>8.7</v>
+        <v>9.4</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0089</v>
+        <v>0.0096</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,25 +885,25 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="K6" s="2">
-        <v>0.0127</v>
+        <v>0.0135</v>
       </c>
       <c r="L6" s="1">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="M6" s="2">
-        <v>0.0127</v>
+        <v>0.0135</v>
       </c>
       <c r="N6" s="1">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O6" s="1">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="P6" s="1">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="Q6" s="2">
         <v>0.033</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0089</v>
+        <v>0.0096</v>
       </c>
       <c r="U6" s="5">
-        <v>9.861</v>
+        <v>9.868</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
@@ -927,16 +927,16 @@
         <v/>
       </c>
       <c r="X6" s="2">
-        <v>-0.0112</v>
+        <v>-0.0105</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0834</v>
+        <v>-0.0828</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0882</v>
+        <v>0.089</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3094</v>
+        <v>0.3103</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>791.6</v>
+        <v>791.8</v>
       </c>
       <c r="D8" s="1">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0062</v>
+        <v>0.0065</v>
       </c>
       <c r="L8" s="1">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0062</v>
+        <v>0.0065</v>
       </c>
       <c r="N8" s="1">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O8" s="1">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P8" s="1">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0265</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0028</v>
+        <v>0.003</v>
       </c>
       <c r="U8" s="5">
-        <v>3.958</v>
+        <v>3.959</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1516</v>
+        <v>0.1519</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2093</v>
+        <v>0.2096</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2714</v>
+        <v>0.2718</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9949</v>
+        <v>0.9954</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>20267.8</v>
+        <v>20273.4</v>
       </c>
       <c r="D9" s="1">
-        <v>-79.8</v>
+        <v>-74.2</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0039</v>
+        <v>-0.0036</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-109.84</v>
+        <v>-104.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0054</v>
+        <v>-0.0051</v>
       </c>
       <c r="L9" s="1">
-        <v>-109.84</v>
+        <v>-104.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0054</v>
+        <v>-0.0051</v>
       </c>
       <c r="N9" s="1">
-        <v>-129.44</v>
+        <v>-135.04</v>
       </c>
       <c r="O9" s="1">
-        <v>-129.44</v>
+        <v>-135.04</v>
       </c>
       <c r="P9" s="1">
-        <v>-129.44</v>
+        <v>-135.04</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6774</v>
@@ -1164,28 +1164,28 @@
         <v>2</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0039</v>
+        <v>-0.0036</v>
       </c>
       <c r="U9" s="5">
-        <v>14.477</v>
+        <v>14.481</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0054</v>
+        <v>0.0051</v>
       </c>
       <c r="X9" s="2">
-        <v>0.0355</v>
+        <v>0.0358</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0087</v>
+        <v>-0.0084</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.061</v>
+        <v>0.0613</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.2121</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>666</v>
+        <v>664.8</v>
       </c>
       <c r="D10" s="1">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0012</v>
+        <v>-0.0006</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,16 +1217,16 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-6.1</v>
+        <v>-7.3</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0109</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.1</v>
+        <v>-7.3</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0091</v>
+        <v>-0.0109</v>
       </c>
       <c r="N10" s="1">
         <v>-6.1</v>
@@ -1238,7 +1238,7 @@
         <v>-6.1</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0223</v>
+        <v>0.0222</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>2</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0012</v>
+        <v>-0.0006</v>
       </c>
       <c r="U10" s="5">
-        <v>1.665</v>
+        <v>1.662</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.009</v>
+        <v>0.0108</v>
       </c>
       <c r="X10" s="2">
-        <v>0.0309</v>
+        <v>0.0291</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2867</v>
+        <v>0.2844</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3681</v>
+        <v>0.3657</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.3039</v>
+        <v>0.3015</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>872.8</v>
+        <v>874.8</v>
       </c>
       <c r="D11" s="1">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0154</v>
+        <v>0.0177</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,16 +1300,16 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>12.3</v>
+        <v>14.3</v>
       </c>
       <c r="K11" s="2">
-        <v>0.0143</v>
+        <v>0.0166</v>
       </c>
       <c r="L11" s="1">
-        <v>12.3</v>
+        <v>14.3</v>
       </c>
       <c r="M11" s="2">
-        <v>0.0143</v>
+        <v>0.0166</v>
       </c>
       <c r="N11" s="1">
         <v>11.5</v>
@@ -1330,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0154</v>
+        <v>0.0177</v>
       </c>
       <c r="U11" s="5">
-        <v>2.182</v>
+        <v>2.187</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
@@ -1342,16 +1342,16 @@
         <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0686</v>
+        <v>0.071</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0356</v>
+        <v>0.0379</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.2042</v>
+        <v>0.207</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.3193</v>
+        <v>0.3223</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29912.4</v>
+        <v>29918.2</v>
       </c>
       <c r="D12" s="1">
-        <v>-52.2</v>
+        <v>-46.4</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0017</v>
+        <v>-0.0015</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-79.39</v>
+        <v>-73.59</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0026</v>
+        <v>-0.0025</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-101.89</v>
+        <v>-110.69</v>
       </c>
       <c r="O12" s="1">
-        <v>-101.89</v>
+        <v>-110.69</v>
       </c>
       <c r="P12" s="1">
-        <v>-101.89</v>
+        <v>-110.69</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9997</v>
